--- a/02.company_data.xlsx
+++ b/02.company_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hey!\Downloads\Practice datasets for data cleaning\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hey!\OneDrive\Desktop\Data_cleaning_Using_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2A87EBD-8849-4634-88D4-928644D492FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97CF48C5-2847-4A6E-80D0-391BC765EC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D330D072-E3E4-4DC1-B84D-61912778608A}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="132">
   <si>
     <t>Date</t>
   </si>
@@ -305,9 +305,6 @@
     <t>Harley        Fritz</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t xml:space="preserve">the procter &amp; gamble company </t>
   </si>
   <si>
@@ -356,9 +353,6 @@
     <t>Conor Wise</t>
   </si>
   <si>
-    <t xml:space="preserve">mcdonald's corporation </t>
-  </si>
-  <si>
     <t>Steven     Michael</t>
   </si>
   <si>
@@ -401,9 +395,6 @@
     <t xml:space="preserve">intel corporation </t>
   </si>
   <si>
-    <t>Jaylynn   Napp</t>
-  </si>
-  <si>
     <t xml:space="preserve">general motors company </t>
   </si>
   <si>
@@ -446,7 +437,16 @@
     <t xml:space="preserve">lockheed martin corporation </t>
   </si>
   <si>
-    <t>Profit_cleaened</t>
+    <t xml:space="preserve">mcdo0ld's corporation </t>
+  </si>
+  <si>
+    <t>Jaylynn   0pp</t>
+  </si>
+  <si>
+    <t>Mik 0am</t>
+  </si>
+  <si>
+    <t>Profit_Margin</t>
   </si>
 </sst>
 </file>
@@ -455,7 +455,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="171" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -501,13 +501,12 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -516,15 +515,6 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="13">
-    <dxf>
-      <numFmt numFmtId="171" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="171" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -539,6 +529,15 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -607,15 +606,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8F491BC7-F642-4C7C-B47C-DDF06BE8F39C}" name="cleaned_dataset" displayName="cleaned_dataset" ref="A1:I32" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:I32" xr:uid="{8F491BC7-F642-4C7C-B47C-DDF06BE8F39C}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{44910AAE-A25B-42BD-BC5D-51FEF847647D}" uniqueName="1" name="Date" queryTableFieldId="1" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{B51DD2E1-E198-4B85-A775-D62D9BE3E8F8}" uniqueName="10" name="Client.1" queryTableFieldId="10" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{58616499-F060-41B5-8F90-24008D89153A}" uniqueName="3" name="Contact" queryTableFieldId="3" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{8DBF5730-BBC7-41C1-898F-46C09E2E6DEF}" uniqueName="4" name="Department" queryTableFieldId="4" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{BD299049-63E1-46C2-91CA-5D4DBF8090F7}" uniqueName="11" name="region" queryTableFieldId="11" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{9171F393-F34F-4DCD-B87C-620B2B65ED73}" uniqueName="5" name="Payment" queryTableFieldId="5" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{06EB784C-63BC-4773-BC03-4A44F9718254}" uniqueName="6" name="Revenue" queryTableFieldId="6" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{225AE735-2DA3-4A60-97FA-769168453778}" uniqueName="7" name="Profit" queryTableFieldId="7" dataDxfId="0"/>
-    <tableColumn id="13" xr3:uid="{BBE848B7-8E19-4571-87D0-A2074D77BE66}" uniqueName="13" name="Profit_cleaened" queryTableFieldId="15" dataCellStyle="Comma"/>
+    <tableColumn id="1" xr3:uid="{44910AAE-A25B-42BD-BC5D-51FEF847647D}" uniqueName="1" name="Date" queryTableFieldId="1" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{B51DD2E1-E198-4B85-A775-D62D9BE3E8F8}" uniqueName="10" name="Client.1" queryTableFieldId="10" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{58616499-F060-41B5-8F90-24008D89153A}" uniqueName="3" name="Contact" queryTableFieldId="3" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{8DBF5730-BBC7-41C1-898F-46C09E2E6DEF}" uniqueName="4" name="Department" queryTableFieldId="4" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{BD299049-63E1-46C2-91CA-5D4DBF8090F7}" uniqueName="11" name="region" queryTableFieldId="11" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{9171F393-F34F-4DCD-B87C-620B2B65ED73}" uniqueName="5" name="Payment" queryTableFieldId="5" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{06EB784C-63BC-4773-BC03-4A44F9718254}" uniqueName="6" name="Revenue" queryTableFieldId="6" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{225AE735-2DA3-4A60-97FA-769168453778}" uniqueName="7" name="Profit" queryTableFieldId="7" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{BBE848B7-8E19-4571-87D0-A2074D77BE66}" uniqueName="13" name="Profit_Margin" queryTableFieldId="15" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -625,11 +624,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4B82C686-FFC9-4647-98EA-BC6EB46B1496}" name="uncleaned_dataset" displayName="uncleaned_dataset" ref="A1:H41" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:H41" xr:uid="{4B82C686-FFC9-4647-98EA-BC6EB46B1496}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{939C026A-A066-4128-85F7-60DFB303BC9C}" uniqueName="1" name="Date" queryTableFieldId="1" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{B9B2262C-9C3C-450A-80BC-0CE5069A2BCF}" uniqueName="2" name="Client" queryTableFieldId="2" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{34874784-16F8-4104-AAA7-791520A24C65}" uniqueName="3" name="Contact" queryTableFieldId="3" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{6781A93D-E137-42F1-8561-92167FF2786F}" uniqueName="4" name="Department" queryTableFieldId="4" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{76CB994F-02DD-40B9-BD52-B3A2A3831A56}" uniqueName="5" name="Payment" queryTableFieldId="5" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{939C026A-A066-4128-85F7-60DFB303BC9C}" uniqueName="1" name="Date" queryTableFieldId="1" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{B9B2262C-9C3C-450A-80BC-0CE5069A2BCF}" uniqueName="2" name="Client" queryTableFieldId="2" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{34874784-16F8-4104-AAA7-791520A24C65}" uniqueName="3" name="Contact" queryTableFieldId="3" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{6781A93D-E137-42F1-8561-92167FF2786F}" uniqueName="4" name="Department" queryTableFieldId="4" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{76CB994F-02DD-40B9-BD52-B3A2A3831A56}" uniqueName="5" name="Payment" queryTableFieldId="5" dataDxfId="0"/>
     <tableColumn id="6" xr3:uid="{C032D50C-2451-4285-A2B0-E942CA0C9A13}" uniqueName="6" name="Revenue" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{354F88E8-1303-41BE-807D-D69CFC2C5E5D}" uniqueName="7" name="Profit" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{0F9D8431-91E3-452E-AF35-BF2A09C084F4}" uniqueName="8" name="Profit Margin" queryTableFieldId="8"/>
@@ -938,16 +937,16 @@
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.7265625" customWidth="1"/>
     <col min="2" max="2" width="27.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.7265625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="10.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.36328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7265625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="10.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.1796875" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -970,13 +969,13 @@
       <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>131</v>
       </c>
       <c r="J1"/>
@@ -985,28 +984,28 @@
       <c r="A2" s="1">
         <v>45076</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="5">
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="4">
         <v>4500</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <v>598</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="3">
         <f>G2/H2</f>
         <v>7.5250836120401337</v>
       </c>
@@ -1016,28 +1015,28 @@
       <c r="A3" s="1">
         <v>45076</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>78</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>81</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="4">
         <v>3800</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>1045</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="3">
         <v>3.6363636363636362</v>
       </c>
       <c r="J3"/>
@@ -1046,28 +1045,28 @@
       <c r="A4" s="1">
         <v>45076</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>81</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
         <v>3712.5</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>1009</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="3">
         <v>3.6793855302279486</v>
       </c>
       <c r="J4"/>
@@ -1076,29 +1075,29 @@
       <c r="A5" s="1">
         <v>45076</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="H5" s="5">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
         <v>779</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>84</v>
+      <c r="I5" s="3">
+        <v>0</v>
       </c>
       <c r="J5"/>
     </row>
@@ -1106,58 +1105,58 @@
       <c r="A6" s="1">
         <v>45076</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="B6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" t="s">
         <v>86</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="4">
         <v>5000</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>684</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="3">
         <v>7.3099415204678362</v>
       </c>
-      <c r="J6" s="6"/>
+      <c r="J6" s="5"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>45077</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
         <v>89</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" t="s">
         <v>77</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="5">
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="4">
         <v>6100</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>544</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="3">
         <v>11.213235294117647</v>
       </c>
       <c r="J7"/>
@@ -1166,28 +1165,28 @@
       <c r="A8" s="1">
         <v>45077</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" t="s">
         <v>77</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="5">
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="4">
         <v>4625</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>670</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="3">
         <v>6.9029850746268657</v>
       </c>
       <c r="J8"/>
@@ -1196,28 +1195,28 @@
       <c r="A9" s="1">
         <v>45077</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" t="s">
         <v>93</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" t="s">
         <v>77</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="5">
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="4">
         <v>3800</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>2045</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="3">
         <v>1.8581907090464547</v>
       </c>
       <c r="J9"/>
@@ -1226,28 +1225,28 @@
       <c r="A10" s="1">
         <v>45077</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="B10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" t="s">
         <v>77</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <v>3600</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>1564</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="3">
         <v>2.3017902813299234</v>
       </c>
       <c r="J10"/>
@@ -1256,28 +1255,28 @@
       <c r="A11" s="1">
         <v>45077</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="B11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" t="s">
         <v>77</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="4">
         <v>5100</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>1220</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="3">
         <v>4.1803278688524594</v>
       </c>
       <c r="J11"/>
@@ -1286,28 +1285,28 @@
       <c r="A12" s="1">
         <v>45077</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" t="s">
         <v>77</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="4">
         <v>4750</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>1435</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="3">
         <v>3.3101045296167246</v>
       </c>
       <c r="J12"/>
@@ -1316,28 +1315,28 @@
       <c r="A13" s="1">
         <v>45077</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="5">
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="4">
         <v>6000</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <v>998</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="3">
         <v>6.0120240480961922</v>
       </c>
       <c r="J13"/>
@@ -1346,28 +1345,28 @@
       <c r="A14" s="1">
         <v>45077</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" t="s">
         <v>102</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="4">
         <v>4500</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
         <v>780</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I14" s="3">
         <v>5.7692307692307692</v>
       </c>
       <c r="J14"/>
@@ -1376,29 +1375,29 @@
       <c r="A15" s="1">
         <v>45078</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="B15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="D15" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" t="s">
+        <v>102</v>
+      </c>
+      <c r="F15" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="H15" s="5">
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
         <v>1044</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>84</v>
+      <c r="I15" s="3">
+        <v>0</v>
       </c>
       <c r="J15"/>
     </row>
@@ -1406,28 +1405,28 @@
       <c r="A16" s="1">
         <v>45078</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="B16" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="5">
+      <c r="C16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="4">
         <v>3712.5</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
         <v>1222</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="3">
         <v>3.0380523731587563</v>
       </c>
       <c r="J16"/>
@@ -1436,28 +1435,28 @@
       <c r="A17" s="1">
         <v>45078</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="5">
+      <c r="B17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="4">
         <v>4950</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="4">
         <v>1065</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I17" s="3">
         <v>4.647887323943662</v>
       </c>
       <c r="J17"/>
@@ -1466,28 +1465,28 @@
       <c r="A18" s="1">
         <v>45078</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="B18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="5">
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="4">
         <v>4750</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="4">
         <v>810</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18" s="3">
         <v>5.8641975308641978</v>
       </c>
       <c r="J18"/>
@@ -1496,28 +1495,28 @@
       <c r="A19" s="1">
         <v>45078</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="B19" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" t="s">
         <v>86</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" s="5">
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="4">
         <v>7320</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="4">
         <v>933</v>
       </c>
-      <c r="I19" s="4">
+      <c r="I19" s="3">
         <v>7.845659163987138</v>
       </c>
       <c r="J19"/>
@@ -1526,28 +1525,28 @@
       <c r="A20" s="1">
         <v>45077</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" t="s">
         <v>99</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" t="s">
         <v>86</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" s="5">
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="4">
         <v>6000</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="4">
         <v>998</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I20" s="3">
         <v>6.0120240480961922</v>
       </c>
       <c r="J20"/>
@@ -1556,28 +1555,28 @@
       <c r="A21" s="1">
         <v>45077</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" t="s">
         <v>101</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="E21" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="4">
         <v>4500</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="4">
         <v>780</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="3">
         <v>5.7692307692307692</v>
       </c>
       <c r="J21"/>
@@ -1586,28 +1585,28 @@
       <c r="A22" s="1">
         <v>45078</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" s="5">
+      <c r="B22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" t="s">
+        <v>101</v>
+      </c>
+      <c r="E22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="4">
         <v>5087.5</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="4">
         <v>655</v>
       </c>
-      <c r="I22" s="4">
+      <c r="I22" s="3">
         <v>7.7671755725190836</v>
       </c>
       <c r="J22"/>
@@ -1616,28 +1615,28 @@
       <c r="A23" s="1">
         <v>45078</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" s="5">
+      <c r="B23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="4">
         <v>4500</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="4">
         <v>722</v>
       </c>
-      <c r="I23" s="4">
+      <c r="I23" s="3">
         <v>6.2326869806094187</v>
       </c>
       <c r="J23"/>
@@ -1646,28 +1645,28 @@
       <c r="A24" s="1">
         <v>45078</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="B24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" t="s">
+        <v>115</v>
+      </c>
+      <c r="D24" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" t="s">
         <v>32</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="4">
         <v>4250</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="4">
         <v>901</v>
       </c>
-      <c r="I24" s="4">
+      <c r="I24" s="3">
         <v>4.716981132075472</v>
       </c>
       <c r="J24"/>
@@ -1676,28 +1675,28 @@
       <c r="A25" s="1">
         <v>45079</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="B25" t="s">
+        <v>116</v>
+      </c>
+      <c r="C25" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" t="s">
+        <v>102</v>
+      </c>
+      <c r="F25" t="s">
         <v>15</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="4">
         <v>5250</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="4">
         <v>1349</v>
       </c>
-      <c r="I25" s="4">
+      <c r="I25" s="3">
         <v>3.8917716827279465</v>
       </c>
       <c r="J25"/>
@@ -1706,28 +1705,28 @@
       <c r="A26" s="1">
         <v>45079</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="B26" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" t="s">
         <v>81</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" t="s">
         <v>15</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="4">
         <v>6500</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="4">
         <v>1288</v>
       </c>
-      <c r="I26" s="4">
+      <c r="I26" s="3">
         <v>5.0465838509316772</v>
       </c>
       <c r="J26"/>
@@ -1736,28 +1735,28 @@
       <c r="A27" s="1">
         <v>45079</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D27" s="2" t="s">
+      <c r="B27" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" t="s">
         <v>80</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" t="s">
         <v>81</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="4">
         <v>7500</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="4">
         <v>1664</v>
       </c>
-      <c r="I27" s="4">
+      <c r="I27" s="3">
         <v>4.5072115384615383</v>
       </c>
       <c r="J27"/>
@@ -1766,28 +1765,28 @@
       <c r="A28" s="1">
         <v>45079</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="B28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" t="s">
         <v>80</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" t="s">
         <v>81</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28" s="5">
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="4">
         <v>5500</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="4">
         <v>1320</v>
       </c>
-      <c r="I28" s="4">
+      <c r="I28" s="3">
         <v>4.166666666666667</v>
       </c>
       <c r="J28"/>
@@ -1796,28 +1795,28 @@
       <c r="A29" s="1">
         <v>45079</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D29" s="2" t="s">
+      <c r="B29" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" t="s">
         <v>80</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" t="s">
         <v>81</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="5">
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="4">
         <v>4625</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="4">
         <v>1001</v>
       </c>
-      <c r="I29" s="4">
+      <c r="I29" s="3">
         <v>4.6203796203796204</v>
       </c>
       <c r="J29"/>
@@ -1826,28 +1825,28 @@
       <c r="A30" s="1">
         <v>45079</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="B30" t="s">
+        <v>125</v>
+      </c>
+      <c r="C30" t="s">
+        <v>126</v>
+      </c>
+      <c r="D30" t="s">
         <v>80</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" t="s">
         <v>81</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G30" s="5">
+      <c r="F30" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="4">
         <v>4500</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="4">
         <v>960</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I30" s="3">
         <v>4.6875</v>
       </c>
       <c r="J30"/>
@@ -1856,28 +1855,28 @@
       <c r="A31" s="1">
         <v>45079</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" t="s">
         <v>130</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" t="s">
         <v>80</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" t="s">
         <v>81</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" t="s">
         <v>32</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="4">
         <v>5400</v>
       </c>
-      <c r="H31" s="5">
+      <c r="H31" s="4">
         <v>540</v>
       </c>
-      <c r="I31" s="4">
+      <c r="I31" s="3">
         <v>10</v>
       </c>
       <c r="J31"/>
@@ -1886,28 +1885,28 @@
       <c r="A32" s="1">
         <v>45076</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="B32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" t="s">
         <v>22</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" t="s">
         <v>86</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" t="s">
         <v>23</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="4">
         <v>5000</v>
       </c>
-      <c r="H32" s="5">
+      <c r="H32" s="4">
         <v>684</v>
       </c>
-      <c r="I32" s="4">
+      <c r="I32" s="3">
         <v>7.3099415204678362</v>
       </c>
       <c r="J32"/>
@@ -1966,16 +1965,16 @@
       <c r="A2" s="1">
         <v>45076</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2">
@@ -1992,16 +1991,16 @@
       <c r="A3" s="1">
         <v>45076</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>15</v>
       </c>
       <c r="F3">
@@ -2018,16 +2017,15 @@
       <c r="A4" s="1">
         <v>45076</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="2"/>
       <c r="F4">
         <v>3712.5</v>
       </c>
@@ -2042,16 +2040,15 @@
       <c r="A5" s="1">
         <v>45076</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="2"/>
       <c r="G5">
         <v>779</v>
       </c>
@@ -2060,16 +2057,16 @@
       <c r="A6" s="1">
         <v>45076</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>23</v>
       </c>
       <c r="F6">
@@ -2086,16 +2083,16 @@
       <c r="A7" s="1">
         <v>45077</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7">
@@ -2112,16 +2109,16 @@
       <c r="A8" s="1">
         <v>45077</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8">
@@ -2138,16 +2135,16 @@
       <c r="A9" s="1">
         <v>45077</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9">
@@ -2164,16 +2161,16 @@
       <c r="A10" s="1">
         <v>45077</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" t="s">
         <v>32</v>
       </c>
       <c r="F10">
@@ -2190,16 +2187,16 @@
       <c r="A11" s="1">
         <v>45077</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" t="s">
         <v>23</v>
       </c>
       <c r="F11">
@@ -2216,16 +2213,16 @@
       <c r="A12" s="1">
         <v>45077</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" t="s">
         <v>23</v>
       </c>
       <c r="F12">
@@ -2242,16 +2239,16 @@
       <c r="A13" s="1">
         <v>45077</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13">
@@ -2268,16 +2265,16 @@
       <c r="A14" s="1">
         <v>45077</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" t="s">
         <v>23</v>
       </c>
       <c r="F14">
@@ -2294,16 +2291,16 @@
       <c r="A15" s="1">
         <v>45078</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" t="s">
         <v>32</v>
       </c>
       <c r="G15">
@@ -2314,16 +2311,16 @@
       <c r="A16" s="1">
         <v>45078</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" t="s">
         <v>11</v>
       </c>
       <c r="F16">
@@ -2340,16 +2337,16 @@
       <c r="A17" s="1">
         <v>45078</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" t="s">
         <v>11</v>
       </c>
       <c r="F17">
@@ -2366,16 +2363,16 @@
       <c r="A18" s="1">
         <v>45078</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" t="s">
         <v>11</v>
       </c>
       <c r="F18">
@@ -2392,16 +2389,16 @@
       <c r="A19" s="1">
         <v>45078</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" t="s">
         <v>11</v>
       </c>
       <c r="F19">
@@ -2418,16 +2415,16 @@
       <c r="A20" s="1">
         <v>45077</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" t="s">
         <v>11</v>
       </c>
       <c r="F20">
@@ -2444,16 +2441,16 @@
       <c r="A21" s="1">
         <v>45077</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" t="s">
         <v>41</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" t="s">
         <v>23</v>
       </c>
       <c r="F21">
@@ -2470,16 +2467,16 @@
       <c r="A22" s="1">
         <v>45078</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" t="s">
         <v>11</v>
       </c>
       <c r="F22">
@@ -2496,16 +2493,16 @@
       <c r="A23" s="1">
         <v>45078</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" t="s">
         <v>11</v>
       </c>
       <c r="F23">
@@ -2522,16 +2519,16 @@
       <c r="A24" s="1">
         <v>45078</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" t="s">
         <v>32</v>
       </c>
       <c r="F24">
@@ -2548,16 +2545,16 @@
       <c r="A25" s="1">
         <v>45079</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" t="s">
         <v>15</v>
       </c>
       <c r="F25">
@@ -2574,16 +2571,16 @@
       <c r="A26" s="1">
         <v>45079</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" t="s">
         <v>15</v>
       </c>
       <c r="F26">
@@ -2600,16 +2597,16 @@
       <c r="A27" s="1">
         <v>45079</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" t="s">
         <v>15</v>
       </c>
       <c r="F27">
@@ -2626,16 +2623,16 @@
       <c r="A28" s="1">
         <v>45079</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" t="s">
         <v>11</v>
       </c>
       <c r="F28">
@@ -2652,16 +2649,16 @@
       <c r="A29" s="1">
         <v>45079</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" t="s">
         <v>11</v>
       </c>
       <c r="F29">
@@ -2678,16 +2675,16 @@
       <c r="A30" s="1">
         <v>45079</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" t="s">
         <v>69</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" t="s">
         <v>11</v>
       </c>
       <c r="F30">
@@ -2704,16 +2701,16 @@
       <c r="A31" s="1">
         <v>45079</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" t="s">
         <v>70</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" t="s">
         <v>71</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" t="s">
         <v>32</v>
       </c>
       <c r="F31">
@@ -2730,16 +2727,16 @@
       <c r="A32" s="1">
         <v>45076</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" t="s">
         <v>22</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" t="s">
         <v>20</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" t="s">
         <v>23</v>
       </c>
       <c r="F32">
@@ -2752,68 +2749,32 @@
         <v>0.1368</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
